--- a/product_selector_out/STM32F0x0 value Line.xlsx
+++ b/product_selector_out/STM32F0x0 value Line.xlsx
@@ -3603,7 +3603,7 @@
       </c>
       <c r="BM19" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32f070c6.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -7486,9 +7486,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
@@ -7551,14 +7551,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R19" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S19" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="T19" s="6" t="inlineStr">
@@ -7706,19 +7706,19 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW19" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AX19" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY19" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AW19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ19" s="6" t="inlineStr">
@@ -7786,9 +7786,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -8788,7 +8788,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -9284,7 +9284,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>STM32F070RB</t>
+          <t>STM32F030CC</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -9299,14 +9299,14 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>STM32F070RB</t>
+          <t>STM32F030CC</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -9321,14 +9321,14 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>STM32F070RB</t>
+          <t>STM32F030CC</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -9343,14 +9343,14 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Table 27. Switching output I/O current consumption</t>
+          <t>Table 29. Switching output I/O current consumption</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>STM32F030CC</t>
+          <t>STM32F070F6</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -9365,14 +9365,14 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>STM32F030CC</t>
+          <t>STM32F070F6</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -9387,14 +9387,14 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>STM32F030CC</t>
+          <t>STM32F070F6</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -9409,14 +9409,14 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Table 29. Switching output I/O current consumption</t>
+          <t>Table 27. Switching output I/O current consumption</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>STM32F070F6</t>
+          <t>STM32F070C6</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -9438,7 +9438,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>STM32F070F6</t>
+          <t>STM32F070C6</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -9460,7 +9460,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>STM32F070F6</t>
+          <t>STM32F070C6</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -9474,72 +9474,6 @@
         </is>
       </c>
       <c r="D31" t="inlineStr">
-        <is>
-          <t>Table 27. Switching output I/O current consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>STM32F070C6</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>STM32F070C6</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>STM32F070C6</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
         <is>
           <t>Table 27. Switching output I/O current consumption</t>
         </is>

--- a/product_selector_out/STM32F0x0 value Line.xlsx
+++ b/product_selector_out/STM32F0x0 value Line.xlsx
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM22"/>
+  <dimension ref="A1:BN22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.4140625" customWidth="1" min="1" max="1"/>
@@ -567,7 +567,8 @@
     <col width="21.765625" customWidth="1" min="62" max="62"/>
     <col width="18" customWidth="1" min="63" max="63"/>
     <col width="18" customWidth="1" min="64" max="64"/>
-    <col width="52" customWidth="1" min="65" max="65"/>
+    <col width="18" customWidth="1" min="65" max="65"/>
+    <col width="52" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -895,6 +896,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -990,6 +996,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1314,6 +1321,11 @@
       </c>
       <c r="BM12" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f030c6.pdf</t>
         </is>
       </c>
@@ -1641,6 +1653,11 @@
       </c>
       <c r="BM13" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN13" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f030c6.pdf</t>
         </is>
       </c>
@@ -1968,6 +1985,11 @@
       </c>
       <c r="BM14" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN14" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f030c6.pdf</t>
         </is>
       </c>
@@ -2295,6 +2317,11 @@
       </c>
       <c r="BM15" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN15" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f030c6.pdf</t>
         </is>
       </c>
@@ -2622,6 +2649,11 @@
       </c>
       <c r="BM16" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN16" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f030c6.pdf</t>
         </is>
       </c>
@@ -2949,6 +2981,11 @@
       </c>
       <c r="BM17" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN17" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f030c6.pdf</t>
         </is>
       </c>
@@ -3276,6 +3313,11 @@
       </c>
       <c r="BM18" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN18" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f070c6.pdf</t>
         </is>
       </c>
@@ -3606,6 +3648,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BN19" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -3930,6 +3977,11 @@
       </c>
       <c r="BM20" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN20" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f030c6.pdf</t>
         </is>
       </c>
@@ -4257,6 +4309,11 @@
       </c>
       <c r="BM21" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN21" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f070c6.pdf</t>
         </is>
       </c>
@@ -4584,12 +4641,17 @@
       </c>
       <c r="BM22" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN22" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f070c6.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="64">
+  <mergeCells count="65">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AS10:AS11"/>
     <mergeCell ref="AD10:AD11"/>
@@ -4610,16 +4672,14 @@
     <mergeCell ref="BA10:BA11"/>
     <mergeCell ref="BG10:BG11"/>
     <mergeCell ref="Q10:Q11"/>
-    <mergeCell ref="A1:BM8"/>
     <mergeCell ref="AR10:AR11"/>
+    <mergeCell ref="AT10:AT11"/>
     <mergeCell ref="S10:S11"/>
-    <mergeCell ref="AT10:AT11"/>
+    <mergeCell ref="BI10:BI11"/>
     <mergeCell ref="AV10:AV11"/>
-    <mergeCell ref="A9:BM9"/>
     <mergeCell ref="BB10:BB11"/>
-    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="BD10:BD11"/>
-    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="Y10:Z10"/>
     <mergeCell ref="AC10:AC11"/>
     <mergeCell ref="B10:B11"/>
@@ -4632,6 +4692,7 @@
     <mergeCell ref="AQ10:AQ11"/>
     <mergeCell ref="AW10:AW11"/>
     <mergeCell ref="BH10:BH11"/>
+    <mergeCell ref="BN10:BN11"/>
     <mergeCell ref="AY10:AY11"/>
     <mergeCell ref="BK10:BK11"/>
     <mergeCell ref="A10:A11"/>
@@ -4651,7 +4712,9 @@
     <mergeCell ref="U10:V10"/>
     <mergeCell ref="AG10:AG11"/>
     <mergeCell ref="F10:F11"/>
+    <mergeCell ref="A9:BN9"/>
     <mergeCell ref="H10:H11"/>
+    <mergeCell ref="A1:BN8"/>
     <mergeCell ref="T10:T11"/>
     <mergeCell ref="J10:J11"/>
   </mergeCells>
@@ -4679,7 +4742,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM22"/>
+  <dimension ref="A1:BN22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4747,6 +4810,7 @@
     <col width="16" customWidth="1" min="63" max="63"/>
     <col width="16" customWidth="1" min="64" max="64"/>
     <col width="16" customWidth="1" min="65" max="65"/>
+    <col width="16" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5080,6 +5144,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -5175,6 +5244,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -5497,7 +5567,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM12" s="6" t="inlineStr">
+      <c r="BM12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -5824,7 +5899,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM13" s="6" t="inlineStr">
+      <c r="BM13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN13" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -6151,7 +6231,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM14" s="6" t="inlineStr">
+      <c r="BM14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN14" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -6478,7 +6563,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM15" s="6" t="inlineStr">
+      <c r="BM15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN15" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -6805,7 +6895,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM16" s="6" t="inlineStr">
+      <c r="BM16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN16" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -7132,7 +7227,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM17" s="6" t="inlineStr">
+      <c r="BM17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN17" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -7459,7 +7559,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM18" s="6" t="inlineStr">
+      <c r="BM18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN18" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -7791,6 +7896,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BN19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -8113,7 +8223,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM20" s="6" t="inlineStr">
+      <c r="BM20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN20" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8440,7 +8555,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM21" s="6" t="inlineStr">
+      <c r="BM21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN21" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8767,7 +8887,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM22" s="6" t="inlineStr">
+      <c r="BM22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN22" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8775,8 +8900,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:BM9"/>
-    <mergeCell ref="A1:BM8"/>
+    <mergeCell ref="A9:BN9"/>
+    <mergeCell ref="A1:BN8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
